--- a/docs/case_files/CASE_TUT.xlsx
+++ b/docs/case_files/CASE_TUT.xlsx
@@ -22,9 +22,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -51,7 +52,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +84,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -96,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -110,6 +116,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -475,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -496,7 +506,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -588,7 +597,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
@@ -686,7 +694,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
@@ -816,7 +823,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
@@ -857,6 +863,94 @@
       <c r="B39" t="inlineStr">
         <is>
           <t>PENDING — Nansen LOCKED, operator feed</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>S1 VENUE DISCOVERY (05/08)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Binance spot TUTUSDT: LISTED! vol $0.23-7.16M/day. CoinGecko tickers: 24 markets (Gate/MEXC/LBank $16-84M — SUSPICIOUS wash). Alpha_117: 400 error (defunct).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>venue_top</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Binance_spot_TUTUSDT (confirmed via api.binance.com)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>spot_perp_ratio_campaign</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0.169x avg (Binance spot $30M + DEX $5M vs perp $207M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>taker_spot_avg</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>50.8% (neutral — no clear distribution signal from taker alone)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cua_A_capacity_day</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>$426k/day (30% of $1.42M avg spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cua_A_total_27d_max</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>$11.5M possible spot distribution in 27 days (upper bound)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>S3_verdict</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS: taker neutral, no DEX large sell pattern visible. On-chain balance PENDING.</t>
         </is>
       </c>
     </row>
@@ -5368,12 +5462,18 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB64" t="n">
+        <v>290000</v>
+      </c>
+      <c r="AC64" s="13" t="n">
+        <v>0.52</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -5434,12 +5534,18 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB65" t="n">
+        <v>400000</v>
+      </c>
+      <c r="AC65" s="13" t="n">
+        <v>0.524</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5606,18 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB66" t="n">
+        <v>280000</v>
+      </c>
+      <c r="AC66" s="13" t="n">
+        <v>0.644</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -5566,12 +5678,18 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB67" t="n">
+        <v>350000</v>
+      </c>
+      <c r="AC67" s="13" t="n">
+        <v>0.522</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -5632,12 +5750,18 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB68" t="n">
+        <v>750000</v>
+      </c>
+      <c r="AC68" s="13" t="n">
+        <v>0.487</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -5698,12 +5822,18 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB69" t="n">
+        <v>650000</v>
+      </c>
+      <c r="AC69" s="13" t="n">
+        <v>0.528</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -5764,8 +5894,14 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB70" t="n">
+        <v>690000</v>
+      </c>
+      <c r="AC70" s="13" t="n">
+        <v>0.476</v>
       </c>
       <c r="AM70" s="11" t="n"/>
       <c r="AN70" t="inlineStr">
@@ -5775,7 +5911,7 @@
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -5836,8 +5972,14 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB71" t="n">
+        <v>230000</v>
+      </c>
+      <c r="AC71" s="13" t="n">
+        <v>0.461</v>
       </c>
       <c r="AM71" s="11" t="n"/>
       <c r="AN71" t="inlineStr">
@@ -5847,7 +5989,7 @@
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -5908,8 +6050,14 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB72" t="n">
+        <v>1060000</v>
+      </c>
+      <c r="AC72" s="14" t="n">
+        <v>0.548</v>
       </c>
       <c r="AM72" s="11" t="n"/>
       <c r="AN72" t="inlineStr">
@@ -5919,7 +6067,7 @@
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -5980,8 +6128,14 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB73" t="n">
+        <v>470000</v>
+      </c>
+      <c r="AC73" s="13" t="n">
+        <v>0.57</v>
       </c>
       <c r="AM73" s="11" t="n"/>
       <c r="AN73" t="inlineStr">
@@ -5991,7 +6145,7 @@
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -6052,12 +6206,18 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB74" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="AC74" s="14" t="n">
+        <v>0.549</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -6118,8 +6278,14 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB75" t="n">
+        <v>1030000</v>
+      </c>
+      <c r="AC75" s="13" t="n">
+        <v>0.464</v>
       </c>
       <c r="AM75" s="11" t="n"/>
       <c r="AN75" t="inlineStr">
@@ -6129,7 +6295,7 @@
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6356,18 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB76" t="n">
+        <v>610000</v>
+      </c>
+      <c r="AC76" s="13" t="n">
+        <v>0.547</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -6256,12 +6428,18 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB77" t="n">
+        <v>350000</v>
+      </c>
+      <c r="AC77" s="13" t="n">
+        <v>0.504</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -6322,12 +6500,18 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB78" t="n">
+        <v>400000</v>
+      </c>
+      <c r="AC78" s="13" t="n">
+        <v>0.479</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -6388,12 +6572,18 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB79" t="n">
+        <v>380000</v>
+      </c>
+      <c r="AC79" s="13" t="n">
+        <v>0.511</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -6454,12 +6644,18 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB80" t="n">
+        <v>510000</v>
+      </c>
+      <c r="AC80" s="13" t="n">
+        <v>0.548</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -6520,12 +6716,18 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB81" t="n">
+        <v>360000</v>
+      </c>
+      <c r="AC81" s="13" t="n">
+        <v>0.51</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -6586,12 +6788,18 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB82" t="n">
+        <v>180000</v>
+      </c>
+      <c r="AC82" s="13" t="n">
+        <v>0.379</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -6652,12 +6860,18 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB83" t="n">
+        <v>940000</v>
+      </c>
+      <c r="AC83" s="13" t="n">
+        <v>0.569</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -6718,12 +6932,18 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB84" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="AC84" s="13" t="n">
+        <v>0.518</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -6784,12 +7004,18 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB85" t="n">
+        <v>1030000</v>
+      </c>
+      <c r="AC85" s="13" t="n">
+        <v>0.523</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -6850,12 +7076,18 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB86" t="n">
+        <v>420000</v>
+      </c>
+      <c r="AC86" s="15" t="n">
+        <v>0.441</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>freshwatch/derived_1h</t>
+          <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -6906,11 +7138,15 @@
       </c>
       <c r="AA87" s="4" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
-      </c>
-      <c r="AB87" s="4" t="n"/>
-      <c r="AC87" s="4" t="n"/>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB87" s="4" t="n">
+        <v>450000</v>
+      </c>
+      <c r="AC87" s="16" t="n">
+        <v>0.491</v>
+      </c>
       <c r="AD87" s="4" t="n"/>
       <c r="AE87" s="4" t="n"/>
       <c r="AF87" s="4" t="n"/>
@@ -6924,7 +7160,7 @@
       <c r="AN87" s="4" t="n"/>
       <c r="AO87" s="4" t="inlineStr">
         <is>
-          <t>fapi_klines_only</t>
+          <t>fapi_klines_only+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -6975,11 +7211,15 @@
       </c>
       <c r="AA88" s="4" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
-      </c>
-      <c r="AB88" s="4" t="n"/>
-      <c r="AC88" s="4" t="n"/>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB88" s="4" t="n">
+        <v>730000</v>
+      </c>
+      <c r="AC88" s="16" t="n">
+        <v>0.51</v>
+      </c>
       <c r="AD88" s="4" t="n"/>
       <c r="AE88" s="4" t="n"/>
       <c r="AF88" s="4" t="n"/>
@@ -6993,7 +7233,7 @@
       <c r="AN88" s="4" t="n"/>
       <c r="AO88" s="4" t="inlineStr">
         <is>
-          <t>fapi_klines_only</t>
+          <t>fapi_klines_only+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -7044,11 +7284,15 @@
       </c>
       <c r="AA89" s="4" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
-      </c>
-      <c r="AB89" s="4" t="n"/>
-      <c r="AC89" s="4" t="n"/>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB89" s="4" t="n">
+        <v>460000</v>
+      </c>
+      <c r="AC89" s="16" t="n">
+        <v>0.492</v>
+      </c>
       <c r="AD89" s="4" t="n"/>
       <c r="AE89" s="4" t="n"/>
       <c r="AF89" s="4" t="n"/>
@@ -7062,7 +7306,7 @@
       <c r="AN89" s="4" t="n"/>
       <c r="AO89" s="4" t="inlineStr">
         <is>
-          <t>fapi_klines_only</t>
+          <t>fapi_klines_only+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7367,18 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB90" t="n">
+        <v>600000</v>
+      </c>
+      <c r="AC90" s="13" t="n">
+        <v>0.497</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>freshwatch/native_1d</t>
+          <t>freshwatch/native_1d+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -7189,12 +7439,18 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB91" t="n">
+        <v>930000</v>
+      </c>
+      <c r="AC91" s="13" t="n">
+        <v>0.578</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>freshwatch/native_1d</t>
+          <t>freshwatch/native_1d+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -7255,12 +7511,18 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB92" t="n">
+        <v>860000</v>
+      </c>
+      <c r="AC92" s="13" t="n">
+        <v>0.502</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>freshwatch/native_1d</t>
+          <t>freshwatch/native_1d+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -7321,12 +7583,18 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB93" t="n">
+        <v>420000</v>
+      </c>
+      <c r="AC93" s="13" t="n">
+        <v>0.466</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>freshwatch/native_1d</t>
+          <t>freshwatch/native_1d+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -7387,12 +7655,18 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB94" t="n">
+        <v>960000</v>
+      </c>
+      <c r="AC94" s="15" t="n">
+        <v>0.442</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>freshwatch/native_1d</t>
+          <t>freshwatch/native_1d+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7727,18 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB95" t="n">
+        <v>3266272</v>
+      </c>
+      <c r="AC95" s="14" t="n">
+        <v>0.542</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>freshwatch/native_1d</t>
+          <t>freshwatch/native_1d+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -7519,8 +7799,14 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB96" t="n">
+        <v>1163961</v>
+      </c>
+      <c r="AC96" s="13" t="n">
+        <v>0.54</v>
       </c>
       <c r="AM96" s="11" t="n"/>
       <c r="AN96" t="inlineStr">
@@ -7530,7 +7816,7 @@
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>freshwatch/native_1d</t>
+          <t>freshwatch/native_1d+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -7591,12 +7877,18 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB97" t="n">
+        <v>6211822</v>
+      </c>
+      <c r="AC97" s="14" t="n">
+        <v>0.5679999999999999</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>freshwatch/native_1d</t>
+          <t>freshwatch/native_1d+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -7657,8 +7949,14 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB98" t="n">
+        <v>8180835</v>
+      </c>
+      <c r="AC98" s="13" t="n">
+        <v>0.509</v>
       </c>
       <c r="AM98" s="11" t="n"/>
       <c r="AN98" t="inlineStr">
@@ -7668,7 +7966,7 @@
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>freshwatch/native_1d</t>
+          <t>freshwatch/native_1d+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -7723,11 +8021,15 @@
       </c>
       <c r="AA99" s="4" t="inlineStr">
         <is>
-          <t>BSC_DEX_WBNB</t>
-        </is>
-      </c>
-      <c r="AB99" s="4" t="n"/>
-      <c r="AC99" s="4" t="n"/>
+          <t>Binance_spot+BSC_DEX</t>
+        </is>
+      </c>
+      <c r="AB99" s="4" t="n">
+        <v>1479152</v>
+      </c>
+      <c r="AC99" s="15" t="n">
+        <v>0.44</v>
+      </c>
       <c r="AD99" s="4" t="n"/>
       <c r="AE99" s="4" t="n"/>
       <c r="AF99" s="4" t="n"/>
@@ -7741,7 +8043,7 @@
       <c r="AN99" s="4" t="n"/>
       <c r="AO99" s="4" t="inlineStr">
         <is>
-          <t>fapi_klines+oi_rt</t>
+          <t>fapi_klines+oi_rt+spot_klines_Binance</t>
         </is>
       </c>
     </row>
@@ -7778,7 +8080,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -8249,7 +8550,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -8432,7 +8732,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -8711,7 +9010,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -8748,7 +9046,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
@@ -8816,7 +9113,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
@@ -8888,7 +9184,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -8961,7 +9256,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>

--- a/docs/case_files/CASE_TUT.xlsx
+++ b/docs/case_files/CASE_TUT.xlsx
@@ -506,6 +506,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -593,7 +594,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Loai C: tu mua kho spot BSC, ban theo ke hoach khi hype du qua perp (campaign)</t>
+          <t>Campaign HAI CHAN KHO: perp book ~$2M VWAP 0.0108 (ghé-rời 2 lần) + spot kho ~83% supply Loai C (chua monetize). Ket thuc qua Cua A (kho/vol ≤10%) hoac Cua B (short-hedge).</t>
         </is>
       </c>
     </row>
@@ -866,10 +867,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
-    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
@@ -8064,7 +8062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8517,6 +8515,72 @@
       <c r="D22" t="inlineStr">
         <is>
           <t>Can kiem tra next export</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HARVEST_INTO_STRENGTH</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>GHE_ROI_LAN_2: pos_r 4.01→2.07 (−48%), gia +33%, gLSR GIAM 1.44→1.11. KHONG phai L-26 (L-26 = gia sap + gLSR tang). Khuon BANK 19-21/07.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SUA AN NHAN: truoc ghi nham L-26 FIRED — chinh xac la HARVEST-INTO-STRENGTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FUNDING_NEG_SPOT_DUMP</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Funding NEG x2 (12:00 UTC -0.000021, 16:00 UTC -0.000059). Spot close-to-close: 0.02870→0.02450 = −14.6% (DO LON). OI ATH 7.873M (3x band). Khoi phuc PIN 20:00 UTC.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Cua B pattern: funding am sau + OI cao + pos that post-dinh</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>POS_REBUILD_INTRADAY</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>pos_r rebuild 2.07→2.72 (intraday 02:05 UTC). gLSR=1.18, OI co ve ~6.07M tu ATH 7.873M. Spot +4.74% tu open. Taker_spot=63.97% (2h).</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Rebuild dang dien ra — chua xac nhan boi daily cron 01:20 UTC</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="2" max="2"/>
@@ -8699,6 +8763,23 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>HIEN TAI: 3.71x (05/08 fapi). Target: 5x=9.61M; 7x=13.45M. Toc do ~0.5M/day. Loai C n=0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CUA_B_CAMPAIGN_END</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Funding am sau (≤-1.5bps sustained) + OI cao + pos thap hau dinh = campaign ket thuc qua short-hedge (khong ban spot). TUT pattern 08-06.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>WATCH — chua fire (08-06 = pattern dau hieu, chua xac nhan boi pos_r sap ben du sau)</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_TUT.xlsx
+++ b/docs/case_files/CASE_TUT.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -867,7 +866,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
@@ -949,6 +947,92 @@
       <c r="B47" t="inlineStr">
         <is>
           <t>AMBIGUOUS: taker neutral, no DEX large sell pattern visible. On-chain balance PENDING.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>LAYER COVERAGE (R7 21/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>first_nn LSR (freshwatch)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>first_nn OI (fapi 30d)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>N/A-GAP dates (freshwatch)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-07-24, 2026-07-25, 2026-07-26, 2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>N/A-RETENTION rule</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Trước first_nn = N/A-RETENTION (store không cover, không collect)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CORRECTIONS (R8 21/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Gap 24-26/07 nguồn store</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>3 ngày freshwatch drop toàn universe (họ TUT+BTW) — không sửa lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Schema-migration R4 v2.1 partial</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>cols 42-45 = o/h/l/c append (append-only per L-57 R4) · cols 46-47 = vol_alpha/taker_alpha CHƯA-TRA (chờ nhịp 2 R5) · cols 51-52 = vol_spot_ext_usd/spot_ext_venue CHƯA-TRA (chờ nhịp 2 R5) · cols 48-50 reserved. Cột v1 cũ (1-41) KHÔNG đè.</t>
         </is>
       </c>
     </row>
@@ -963,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO99"/>
+  <dimension ref="A1:AZ114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1000,6 +1084,36 @@
           <t>MANUAL (operator)</t>
         </is>
       </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>OHLC-append (R4)</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>vol_alpha-append (R4)</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>reserved</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>reserved</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>reserved</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>SPOT-EXT (v2.1 R4 21/08)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1207,6 +1321,49 @@
           <t>mm_note</t>
         </is>
       </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>vol_alpha</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>taker_alpha</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>vol_spot_ext_usd</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>spot_ext_venue</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1219,15 +1376,23 @@
       </c>
       <c r="C3" s="4" t="n"/>
       <c r="D3" s="4" t="n">
-        <v>746585.20943</v>
+        <v>746585.21</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>0.4744092749513714</v>
-      </c>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
+        <v>47.4624</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
@@ -1274,6 +1439,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP3" t="n">
+        <v>0.01063</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.01085</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.01053</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.01062</v>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1288,15 +1485,23 @@
         <v>0.02919020715630904</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1219863.9298</v>
+        <v>1219863.93</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.4961939696837946</v>
-      </c>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
+        <v>49.6269</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
@@ -1343,6 +1548,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP4" t="n">
+        <v>0.01063</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.01116</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.01047</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.01093</v>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1357,15 +1594,23 @@
         <v>0.06312900274473932</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>11548984.5578</v>
+        <v>11548984.56</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.4793671941468181</v>
-      </c>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
+        <v>47.9691</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
@@ -1412,6 +1657,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP5" t="n">
+        <v>0.01093</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.01245</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.01067</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.01162</v>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1426,15 +1703,23 @@
         <v>0.193631669535284</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>29748918.71993</v>
+        <v>29748918.72</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.4783392832698132</v>
-      </c>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
+        <v>47.8763</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>3.891e-05</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>-1.653e-05</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
@@ -1481,6 +1766,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP6" t="n">
+        <v>0.01162</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.01145</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.01387</v>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1495,15 +1812,23 @@
         <v>-0.05839942321557312</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>10522976.77791</v>
+        <v>10522976.78</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.4689269345139785</v>
-      </c>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
+        <v>46.9423</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>4.939e-05</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>4.631e-05</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J7" s="4" t="n"/>
       <c r="K7" s="4" t="n"/>
       <c r="L7" s="4" t="n"/>
@@ -1550,6 +1875,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP7" t="n">
+        <v>0.01387</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.01456</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.01256</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.01306</v>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1564,15 +1921,23 @@
         <v>-0.01990811638591117</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3420621.97771</v>
+        <v>3420621.98</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0.4552033650652773</v>
-      </c>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
+        <v>45.5497</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
@@ -1619,6 +1984,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP8" t="n">
+        <v>0.01306</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.01345</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.01229</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1633,15 +2030,23 @@
         <v>0.04218749999999982</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5238575.93742</v>
+        <v>5238575.94</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.4901308471697227</v>
-      </c>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
+        <v>49.0385</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>4.922e-05</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>4.533e-05</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J9" s="4" t="n"/>
       <c r="K9" s="4" t="n"/>
       <c r="L9" s="4" t="n"/>
@@ -1688,6 +2093,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP9" t="n">
+        <v>0.01279</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.01401</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.01257</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.01334</v>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1702,15 +2139,23 @@
         <v>0.03373313343328332</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2511883.87934</v>
+        <v>2511883.88</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0.4776618269234058</v>
-      </c>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
+        <v>47.8357</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
@@ -1757,6 +2202,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP10" t="n">
+        <v>0.01334</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.01388</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.01297</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.01379</v>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1771,15 +2248,23 @@
         <v>-0.008701957940536631</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4233592.80755</v>
+        <v>4233592.81</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0.475109062480827</v>
-      </c>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
+        <v>47.5351</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J11" s="4" t="n"/>
       <c r="K11" s="4" t="n"/>
       <c r="L11" s="4" t="n"/>
@@ -1826,6 +2311,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP11" t="n">
+        <v>0.01378</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.01337</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.01367</v>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1840,15 +2357,23 @@
         <v>0.0131675201170447</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2173747.94549</v>
+        <v>2173747.95</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>0.4569859138300282</v>
-      </c>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
+        <v>45.7778</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>4.356e-05</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1.138e-05</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n"/>
       <c r="L12" s="4" t="n"/>
@@ -1895,6 +2420,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP12" t="n">
+        <v>0.01367</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.01402</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.01287</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.01385</v>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1909,15 +2466,23 @@
         <v>0.01877256317689535</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2278312.32189</v>
+        <v>2278312.32</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.4972449347056377</v>
-      </c>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
+        <v>49.7657</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>4.653e-05</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>3.186e-05</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="n"/>
       <c r="L13" s="4" t="n"/>
@@ -1964,6 +2529,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP13" t="n">
+        <v>0.01386</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.01429</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.01411</v>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1978,15 +2575,23 @@
         <v>-0.06449326718639259</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1935206.28047</v>
+        <v>1935206.28</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0.4931077499098226</v>
-      </c>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
+        <v>49.3371</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
@@ -2033,6 +2638,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP14" t="n">
+        <v>0.01411</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.01415</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.01311</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -2047,15 +2684,23 @@
         <v>-0.05075757575757578</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1445381.32448</v>
+        <v>1445381.32</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>0.453213761908107</v>
-      </c>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
+        <v>45.3296</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
       <c r="L15" s="4" t="n"/>
@@ -2102,6 +2747,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP15" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.01382</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.01237</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.01253</v>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2116,15 +2793,23 @@
         <v>0.01276935355147657</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1068903.96557</v>
+        <v>1068903.97</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>0.4617039920166052</v>
-      </c>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
+        <v>46.2006</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>4.034e-05</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>-7.94e-06</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n"/>
@@ -2171,6 +2856,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP16" t="n">
+        <v>0.01252</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0.01308</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.01219</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.01269</v>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2185,15 +2902,23 @@
         <v>-0.04018912529550833</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1796199.36648</v>
+        <v>1796199.37</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0.4487475732991927</v>
-      </c>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
+        <v>44.9371</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>4.808e-05</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>3.849e-05</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="n"/>
       <c r="L17" s="4" t="n"/>
@@ -2240,6 +2965,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP17" t="n">
+        <v>0.01269</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.01313</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.01213</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0.01218</v>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2254,15 +3011,23 @@
         <v>-0.07224958949096882</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1510879.76829</v>
+        <v>1510879.77</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.4364482546380311</v>
-      </c>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
+        <v>43.5985</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4" t="n"/>
@@ -2309,6 +3074,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP18" t="n">
+        <v>0.01218</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.01231</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0.01118</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -2323,15 +3120,23 @@
         <v>-0.02477876106194676</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1382459.17844</v>
+        <v>1382459.18</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.4453916183233281</v>
-      </c>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
+        <v>44.6491</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
@@ -2378,6 +3183,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP19" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.01178</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0.01063</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.01102</v>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2392,15 +3229,23 @@
         <v>0.003629764065335772</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>764301.07526</v>
+        <v>764301.08</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.472380250379785</v>
-      </c>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
+        <v>47.2699</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
@@ -2447,6 +3292,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP20" t="n">
+        <v>0.01102</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.01122</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0.01077</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0.01106</v>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2461,15 +3338,23 @@
         <v>-0.007233273056057921</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3715284.74631</v>
+        <v>3715284.75</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.5122625227021806</v>
-      </c>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
+        <v>51.2949</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>2.857e-05</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>-2.048e-05</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J21" s="4" t="n"/>
       <c r="K21" s="4" t="n"/>
       <c r="L21" s="4" t="n"/>
@@ -2516,6 +3401,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP21" t="n">
+        <v>0.01106</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.01157</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0.01075</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0.01098</v>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2530,15 +3447,23 @@
         <v>0.03187613843351556</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1512900.55684</v>
+        <v>1512900.56</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.5436160490129264</v>
-      </c>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
+        <v>54.4203</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="n"/>
       <c r="L22" s="4" t="n"/>
@@ -2585,6 +3510,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP22" t="n">
+        <v>0.01099</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.01143</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0.01083</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0.01133</v>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -2599,15 +3556,23 @@
         <v>0.04589585172109434</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2353908.2062</v>
+        <v>2353908.21</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0.5301056169175391</v>
-      </c>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
+        <v>53.1009</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J23" s="4" t="n"/>
       <c r="K23" s="4" t="n"/>
       <c r="L23" s="4" t="n"/>
@@ -2654,6 +3619,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP23" t="n">
+        <v>0.01133</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.01204</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.01131</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0.01185</v>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -2668,15 +3665,23 @@
         <v>-0.08523206751054846</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1952507.99827</v>
+        <v>1952508</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>0.5165245756273318</v>
-      </c>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
+        <v>51.8492</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J24" s="4" t="n"/>
       <c r="K24" s="4" t="n"/>
       <c r="L24" s="4" t="n"/>
@@ -2723,6 +3728,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP24" t="n">
+        <v>0.01184</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0.01081</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0.01084</v>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2737,15 +3774,23 @@
         <v>0.02121771217712176</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1652014.46057</v>
+        <v>1652014.46</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>0.5136747741663421</v>
-      </c>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
+        <v>51.5247</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="n"/>
       <c r="L25" s="4" t="n"/>
@@ -2792,6 +3837,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP25" t="n">
+        <v>0.01083</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0.01127</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0.01043</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.01107</v>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -2806,15 +3883,23 @@
         <v>-0.04245709123757901</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>964309.70075</v>
+        <v>964309.7</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>0.5010146087642742</v>
-      </c>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
+        <v>50.191</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J26" s="4" t="n"/>
       <c r="K26" s="4" t="n"/>
       <c r="L26" s="4" t="n"/>
@@ -2861,6 +3946,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP26" t="n">
+        <v>0.01107</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0.01038</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="AT26" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2875,15 +3992,23 @@
         <v>-0.003773584905660377</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1115812.70882</v>
+        <v>1115812.71</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0.5340284477062703</v>
-      </c>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
+        <v>53.512</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J27" s="4" t="n"/>
       <c r="K27" s="4" t="n"/>
       <c r="L27" s="4" t="n"/>
@@ -2930,6 +4055,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP27" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0.01105</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0.01052</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0.01056</v>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -2944,15 +4101,23 @@
         <v>-0.03503787878787878</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1061975.60469</v>
+        <v>1061975.6</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>0.4400066710458599</v>
-      </c>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
+        <v>44.0336</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
       <c r="L28" s="4" t="n"/>
@@ -2999,6 +4164,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP28" t="n">
+        <v>0.01056</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0.01078</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0.01019</v>
+      </c>
+      <c r="AT28" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -3013,15 +4210,23 @@
         <v>-0.01766437684003919</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>866151.78942</v>
+        <v>866151.79</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>0.4519156397762729</v>
-      </c>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
+        <v>45.2782</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J29" s="4" t="n"/>
       <c r="K29" s="4" t="n"/>
       <c r="L29" s="4" t="n"/>
@@ -3068,6 +4273,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP29" t="n">
+        <v>0.01019</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0.01048</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0.009889999999999999</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0.01001</v>
+      </c>
+      <c r="AT29" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -3082,15 +4319,23 @@
         <v>-0.02997002997002995</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1176537.0997</v>
+        <v>1176537.1</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>0.4580489846166928</v>
-      </c>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
+        <v>45.8165</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n"/>
@@ -3137,6 +4382,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP30" t="n">
+        <v>0.01002</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.01009</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0.009429999999999999</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.00971</v>
+      </c>
+      <c r="AT30" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -3151,15 +4428,23 @@
         <v>-0.004119464469618972</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1424311.83523</v>
+        <v>1424311.84</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>0.4797054983381241</v>
-      </c>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
+        <v>47.9825</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J31" s="4" t="n"/>
       <c r="K31" s="4" t="n"/>
       <c r="L31" s="4" t="n"/>
@@ -3206,6 +4491,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP31" t="n">
+        <v>0.009719999999999999</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.009979999999999999</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.00928</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.00967</v>
+      </c>
+      <c r="AT31" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -3220,15 +4537,23 @@
         <v>0.07445708376421933</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1314173.43739</v>
+        <v>1314173.44</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>0.4880591565188828</v>
-      </c>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
+        <v>48.8114</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J32" s="4" t="n"/>
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n"/>
@@ -3275,6 +4600,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP32" t="n">
+        <v>0.00967</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0.01071</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0.00966</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0.01039</v>
+      </c>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -3289,15 +4646,23 @@
         <v>-0.012512030798845</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1282701.69921</v>
+        <v>1282701.7</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0.4674944084263421</v>
-      </c>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
-      <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
+        <v>46.7957</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J33" s="4" t="n"/>
       <c r="K33" s="4" t="n"/>
       <c r="L33" s="4" t="n"/>
@@ -3344,6 +4709,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP33" t="n">
+        <v>0.01039</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.01047</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0.009860000000000001</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0.01026</v>
+      </c>
+      <c r="AT33" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -3358,15 +4755,23 @@
         <v>0.003898635477582957</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1827025.98967</v>
+        <v>1827025.99</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>0.4904669933392489</v>
-      </c>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="n"/>
+        <v>49.0491</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J34" s="4" t="n"/>
       <c r="K34" s="4" t="n"/>
       <c r="L34" s="4" t="n"/>
@@ -3413,6 +4818,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP34" t="n">
+        <v>0.01026</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0.01069</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0.00996</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0.0103</v>
+      </c>
+      <c r="AT34" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -3427,15 +4864,23 @@
         <v>-0.07087378640776698</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1791702.64025</v>
+        <v>1791702.64</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>0.4856705825594717</v>
-      </c>
-      <c r="F35" s="4" t="n"/>
-      <c r="G35" s="4" t="n"/>
-      <c r="H35" s="4" t="n"/>
-      <c r="I35" s="4" t="n"/>
+        <v>48.5484</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J35" s="4" t="n"/>
       <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="n"/>
@@ -3482,6 +4927,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP35" t="n">
+        <v>0.01031</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.01039</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0.00925</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0.00957</v>
+      </c>
+      <c r="AT35" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -3496,15 +4973,23 @@
         <v>0.005224660397074254</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>1419257.26974</v>
+        <v>1419257.27</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.5001792520263615</v>
-      </c>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n"/>
-      <c r="I36" s="4" t="n"/>
+        <v>50.0106</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J36" s="4" t="n"/>
       <c r="K36" s="4" t="n"/>
       <c r="L36" s="4" t="n"/>
@@ -3551,6 +5036,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP36" t="n">
+        <v>0.00957</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0.00923</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0.00962</v>
+      </c>
+      <c r="AT36" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -3565,15 +5082,23 @@
         <v>-0.007276507276507305</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>3542782.53704</v>
+        <v>3542782.54</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>0.5053581965609086</v>
-      </c>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
-      <c r="I37" s="4" t="n"/>
+        <v>50.5729</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="n"/>
       <c r="L37" s="4" t="n"/>
@@ -3620,6 +5145,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP37" t="n">
+        <v>0.00962</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.01004</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0.008529999999999999</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0.009549999999999999</v>
+      </c>
+      <c r="AT37" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -3634,15 +5191,23 @@
         <v>0.09005235602094253</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>10226338.68589</v>
+        <v>10226338.69</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0.4863690174021091</v>
-      </c>
-      <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="n"/>
-      <c r="H38" s="4" t="n"/>
-      <c r="I38" s="4" t="n"/>
+        <v>48.6447</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="n"/>
       <c r="L38" s="4" t="n"/>
@@ -3689,6 +5254,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP38" t="n">
+        <v>0.009549999999999999</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0.01094</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0.00915</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0.01041</v>
+      </c>
+      <c r="AT38" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -3703,15 +5300,23 @@
         <v>0.03170028818443793</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>5590269.85415</v>
+        <v>5590269.85</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.5228116586203426</v>
-      </c>
-      <c r="F39" s="4" t="n"/>
-      <c r="G39" s="4" t="n"/>
-      <c r="H39" s="4" t="n"/>
-      <c r="I39" s="4" t="n"/>
+        <v>52.4441</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="n"/>
       <c r="L39" s="4" t="n"/>
@@ -3758,6 +5363,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP39" t="n">
+        <v>0.01041</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.01086</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0.009220000000000001</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0.01074</v>
+      </c>
+      <c r="AT39" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -3772,15 +5409,23 @@
         <v>-0.06517690875232773</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>4569012.88387</v>
+        <v>4569012.88</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.5245427617141386</v>
-      </c>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
+        <v>52.5909</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="n"/>
       <c r="L40" s="4" t="n"/>
@@ -3827,6 +5472,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP40" t="n">
+        <v>0.01074</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0.01185</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0.00962</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0.01004</v>
+      </c>
+      <c r="AT40" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -3841,15 +5518,23 @@
         <v>0.02091633466135456</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>1857242.70977</v>
+        <v>1857242.71</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0.5087268282689528</v>
-      </c>
-      <c r="F41" s="4" t="n"/>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n"/>
-      <c r="I41" s="4" t="n"/>
+        <v>50.8585</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="n"/>
       <c r="L41" s="4" t="n"/>
@@ -3896,6 +5581,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP41" t="n">
+        <v>0.01004</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0.01054</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0.00957</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0.01025</v>
+      </c>
+      <c r="AT41" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -3910,15 +5627,23 @@
         <v>-0.0204878048780488</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>2032110.94834</v>
+        <v>2032110.95</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>0.4735587890921075</v>
-      </c>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="n"/>
+        <v>47.4191</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n"/>
@@ -3965,6 +5690,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP42" t="n">
+        <v>0.01025</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0.01052</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0.009769999999999999</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0.01004</v>
+      </c>
+      <c r="AT42" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -3979,15 +5736,23 @@
         <v>-0.0009960159362549792</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>1249613.07113</v>
+        <v>1249613.07</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0.4790928155531175</v>
-      </c>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="n"/>
+        <v>47.9388</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>4.354e-05</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>1.124e-05</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J43" s="4" t="n"/>
       <c r="K43" s="4" t="n"/>
       <c r="L43" s="4" t="n"/>
@@ -4034,6 +5799,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP43" t="n">
+        <v>0.01003</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0.01034</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0.009730000000000001</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0.01003</v>
+      </c>
+      <c r="AT43" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -4048,15 +5845,23 @@
         <v>0.007976071784645988</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>1201278.58789</v>
+        <v>1201278.59</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>0.4815333264761451</v>
-      </c>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="4" t="n"/>
+        <v>48.1618</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4" t="n"/>
@@ -4103,6 +5908,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP44" t="n">
+        <v>0.01003</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0.01037</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0.00996</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0.01011</v>
+      </c>
+      <c r="AT44" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -4117,15 +5954,23 @@
         <v>0.06033630069238383</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>2128017.54183</v>
+        <v>2128017.54</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>0.4690905007938523</v>
-      </c>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n"/>
+        <v>47.0013</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
@@ -4172,6 +6017,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP45" t="n">
+        <v>0.01011</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0.01121</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>0.009990000000000001</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>0.01072</v>
+      </c>
+      <c r="AT45" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -4186,15 +6063,23 @@
         <v>-0.01026119402985082</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>1083088.42071</v>
+        <v>1083088.42</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>0.4552967868441293</v>
-      </c>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
+        <v>45.5345</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="n"/>
       <c r="L46" s="4" t="n"/>
@@ -4241,6 +6126,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP46" t="n">
+        <v>0.01074</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>0.01021</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0.01061</v>
+      </c>
+      <c r="AT46" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -4255,15 +6172,23 @@
         <v>0.03487276154571162</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>883546.97013</v>
+        <v>883546.97</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>0.4784500742859923</v>
-      </c>
-      <c r="F47" s="4" t="n"/>
-      <c r="G47" s="4" t="n"/>
-      <c r="H47" s="4" t="n"/>
-      <c r="I47" s="4" t="n"/>
+        <v>47.8391</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J47" s="4" t="n"/>
       <c r="K47" s="4" t="n"/>
       <c r="L47" s="4" t="n"/>
@@ -4310,6 +6235,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP47" t="n">
+        <v>0.01061</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0.01102</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>0.01049</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0.01098</v>
+      </c>
+      <c r="AT47" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -4324,15 +6281,23 @@
         <v>-0.05009107468123863</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>1056676.2875</v>
+        <v>1056676.29</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>0.4844361962176232</v>
-      </c>
-      <c r="F48" s="4" t="n"/>
-      <c r="G48" s="4" t="n"/>
-      <c r="H48" s="4" t="n"/>
-      <c r="I48" s="4" t="n"/>
+        <v>48.4578</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J48" s="4" t="n"/>
       <c r="K48" s="4" t="n"/>
       <c r="L48" s="4" t="n"/>
@@ -4379,6 +6344,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP48" t="n">
+        <v>0.01099</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0.01109</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>0.01033</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>0.01043</v>
+      </c>
+      <c r="AT48" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -4393,15 +6390,23 @@
         <v>0</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>1426111.54435</v>
+        <v>1426111.54</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>0.4557261732777332</v>
-      </c>
-      <c r="F49" s="4" t="n"/>
-      <c r="G49" s="4" t="n"/>
-      <c r="H49" s="4" t="n"/>
-      <c r="I49" s="4" t="n"/>
+        <v>45.5767</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J49" s="4" t="n"/>
       <c r="K49" s="4" t="n"/>
       <c r="L49" s="4" t="n"/>
@@ -4448,6 +6453,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP49" t="n">
+        <v>0.01043</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>0.01097</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>0.01043</v>
+      </c>
+      <c r="AT49" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -4462,15 +6499,23 @@
         <v>-0.002876318312559967</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>1281168.45461</v>
+        <v>1281168.45</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>0.4703539410546384</v>
-      </c>
-      <c r="F50" s="4" t="n"/>
-      <c r="G50" s="4" t="n"/>
-      <c r="H50" s="4" t="n"/>
-      <c r="I50" s="4" t="n"/>
+        <v>47.038</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J50" s="4" t="n"/>
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
@@ -4517,6 +6562,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP50" t="n">
+        <v>0.01044</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>0.01073</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>0.01027</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>0.0104</v>
+      </c>
+      <c r="AT50" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -4531,15 +6608,23 @@
         <v>-0.02596153846153837</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>1635357.05068</v>
+        <v>1635357.05</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>0.5721217944417135</v>
-      </c>
-      <c r="F51" s="4" t="n"/>
-      <c r="G51" s="4" t="n"/>
-      <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="n"/>
+        <v>57.2753</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>4.096e-05</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>-4.22e-06</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J51" s="4" t="n"/>
       <c r="K51" s="4" t="n"/>
       <c r="L51" s="4" t="n"/>
@@ -4586,6 +6671,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP51" t="n">
+        <v>0.01039</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>0.01048</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>0.00993</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>0.01013</v>
+      </c>
+      <c r="AT51" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -4600,15 +6717,23 @@
         <v>0.05725567620927952</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>3496918.25751</v>
+        <v>3496918.26</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>0.4966800433448798</v>
-      </c>
-      <c r="F52" s="4" t="n"/>
-      <c r="G52" s="4" t="n"/>
-      <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="n"/>
+        <v>49.6713</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J52" s="4" t="n"/>
       <c r="K52" s="4" t="n"/>
       <c r="L52" s="4" t="n"/>
@@ -4655,6 +6780,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP52" t="n">
+        <v>0.01013</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>0.01166</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>0.01007</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>0.01071</v>
+      </c>
+      <c r="AT52" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -4669,15 +6826,23 @@
         <v>-0.02054154995331481</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>1213698.59315</v>
+        <v>1213698.59</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>0.5082958623905949</v>
-      </c>
-      <c r="F53" s="4" t="n"/>
-      <c r="G53" s="4" t="n"/>
-      <c r="H53" s="4" t="n"/>
-      <c r="I53" s="4" t="n"/>
+        <v>50.7923</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J53" s="4" t="n"/>
       <c r="K53" s="4" t="n"/>
       <c r="L53" s="4" t="n"/>
@@ -4724,6 +6889,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP53" t="n">
+        <v>0.01071</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>0.01086</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>0.01004</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>0.01049</v>
+      </c>
+      <c r="AT53" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -4738,15 +6935,23 @@
         <v>-0.02192564346997139</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>578118.81935</v>
+        <v>578118.8199999999</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>0.51299651992388</v>
-      </c>
-      <c r="F54" s="4" t="n"/>
-      <c r="G54" s="4" t="n"/>
-      <c r="H54" s="4" t="n"/>
-      <c r="I54" s="4" t="n"/>
+        <v>51.2999</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J54" s="4" t="n"/>
       <c r="K54" s="4" t="n"/>
       <c r="L54" s="4" t="n"/>
@@ -4793,6 +6998,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP54" t="n">
+        <v>0.01049</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>0.01067</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>0.01024</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>0.01026</v>
+      </c>
+      <c r="AT54" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -4807,15 +7044,23 @@
         <v>-0.02436647173489281</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>887409.59513</v>
+        <v>887409.6</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>0.4033007800533309</v>
-      </c>
-      <c r="F55" s="4" t="n"/>
-      <c r="G55" s="4" t="n"/>
-      <c r="H55" s="4" t="n"/>
-      <c r="I55" s="4" t="n"/>
+        <v>40.457</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
@@ -4862,6 +7107,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP55" t="n">
+        <v>0.01026</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>0.01053</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>0.009939999999999999</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>0.01001</v>
+      </c>
+      <c r="AT55" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -4876,15 +7153,23 @@
         <v>0.03996003996004016</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>1580521.99484</v>
+        <v>1580521.99</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>0.5087655274220342</v>
-      </c>
-      <c r="F56" s="4" t="n"/>
-      <c r="G56" s="4" t="n"/>
-      <c r="H56" s="4" t="n"/>
-      <c r="I56" s="4" t="n"/>
+        <v>51.0117</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J56" s="4" t="n"/>
       <c r="K56" s="4" t="n"/>
       <c r="L56" s="4" t="n"/>
@@ -4931,6 +7216,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP56" t="n">
+        <v>0.01001</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>0.01088</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>0.009990000000000001</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>0.01041</v>
+      </c>
+      <c r="AT56" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -4945,15 +7262,23 @@
         <v>-0.007684918347742542</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>2574982.41483</v>
+        <v>2574982.41</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>0.4734159422035461</v>
-      </c>
-      <c r="F57" s="4" t="n"/>
-      <c r="G57" s="4" t="n"/>
-      <c r="H57" s="4" t="n"/>
-      <c r="I57" s="4" t="n"/>
+        <v>47.4133</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="J57" s="4" t="n"/>
       <c r="K57" s="4" t="n"/>
       <c r="L57" s="4" t="n"/>
@@ -5000,6 +7325,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP57" t="n">
+        <v>0.0104</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>0.01104</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>0.00961</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>0.01033</v>
+      </c>
+      <c r="AT57" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -5014,15 +7371,23 @@
         <v>0.03097773475314614</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>2648582.01361</v>
+        <v>2648582.01</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>0.5042010374972129</v>
-      </c>
-      <c r="F58" s="4" t="n"/>
-      <c r="G58" s="4" t="n"/>
-      <c r="H58" s="4" t="n"/>
-      <c r="I58" s="4" t="n"/>
+        <v>50.4723</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>4.109e-05</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>-3.45e-06</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="n"/>
       <c r="L58" s="4" t="n"/>
@@ -5069,6 +7434,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP58" t="n">
+        <v>0.01032</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>0.01116</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>0.009979999999999999</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>0.01065</v>
+      </c>
+      <c r="AT58" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -5083,15 +7480,23 @@
         <v>0.01502347417840388</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>1198191.6053</v>
+        <v>1198191.61</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>0.4845455345809802</v>
-      </c>
-      <c r="F59" s="4" t="n"/>
-      <c r="G59" s="4" t="n"/>
-      <c r="H59" s="4" t="n"/>
-      <c r="I59" s="4" t="n"/>
+        <v>48.4609</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
@@ -5138,6 +7543,38 @@
           <t>fapi_klines_only</t>
         </is>
       </c>
+      <c r="AP59" t="n">
+        <v>0.01064</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>0.01046</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>0.01081</v>
+      </c>
+      <c r="AT59" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5146,16 +7583,16 @@
         </is>
       </c>
       <c r="B60" s="7" t="n">
-        <v>0.0105608783381635</v>
+        <v>0.01025</v>
       </c>
       <c r="C60" s="8" t="n">
         <v>-0.02304548213103608</v>
       </c>
       <c r="D60" t="n">
-        <v>1984330.35294</v>
+        <v>661443.45</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>0.4657676244365678</v>
+        <v>46.6158</v>
       </c>
       <c r="F60" s="9" t="n">
         <v>4.193e-05</v>
@@ -5204,6 +7641,38 @@
           <t>freshwatch/derived_1h</t>
         </is>
       </c>
+      <c r="AP60" t="n">
+        <v>0.01081</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>0.01097</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>0.01021</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>0.01025</v>
+      </c>
+      <c r="AT60" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5212,19 +7681,19 @@
         </is>
       </c>
       <c r="B61" s="7" t="n">
-        <v>0.010537105862997</v>
+        <v>0.01041</v>
       </c>
       <c r="C61" s="8" t="n">
         <v>-0.002250994131860584</v>
       </c>
       <c r="D61" t="n">
-        <v>2527447.68282</v>
+        <v>842482.5600000001</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>0.4864635813310384</v>
+        <v>48.6838</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>4.033666666666667e-05</v>
+        <v>4.034e-05</v>
       </c>
       <c r="G61" s="9" t="n">
         <v>-7.98e-06</v>
@@ -5270,6 +7739,38 @@
           <t>freshwatch/derived_1h</t>
         </is>
       </c>
+      <c r="AP61" t="n">
+        <v>0.01025</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>0.01087</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>0.01023</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>0.01041</v>
+      </c>
+      <c r="AT61" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5278,16 +7779,16 @@
         </is>
       </c>
       <c r="B62" s="7" t="n">
-        <v>0.0105226977810573</v>
+        <v>0.01036</v>
       </c>
       <c r="C62" s="8" t="n">
         <v>-0.001367366156042604</v>
       </c>
       <c r="D62" t="n">
-        <v>2619452.60892</v>
+        <v>873150.87</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>0.4871941552886407</v>
+        <v>48.8094</v>
       </c>
       <c r="F62" s="9" t="n">
         <v>5e-05</v>
@@ -5336,6 +7837,38 @@
           <t>freshwatch/derived_1h</t>
         </is>
       </c>
+      <c r="AP62" t="n">
+        <v>0.0104</v>
+      </c>
+      <c r="AQ62" t="n">
+        <v>0.01078</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>0.01033</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>0.01036</v>
+      </c>
+      <c r="AT62" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5344,16 +7877,16 @@
         </is>
       </c>
       <c r="B63" s="7" t="n">
-        <v>0.010480864572767</v>
+        <v>0.01037</v>
       </c>
       <c r="C63" s="8" t="n">
         <v>-0.003975521217154721</v>
       </c>
       <c r="D63" t="n">
-        <v>3715360.22556</v>
+        <v>1238453.41</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>0.4718677570508022</v>
+        <v>47.2328</v>
       </c>
       <c r="F63" s="9" t="n">
         <v>5e-05</v>
@@ -5402,6 +7935,38 @@
           <t>freshwatch/derived_1h</t>
         </is>
       </c>
+      <c r="AP63" t="n">
+        <v>0.01035</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>0.01098</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>0.01021</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>0.01037</v>
+      </c>
+      <c r="AT63" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5410,16 +7975,16 @@
         </is>
       </c>
       <c r="B64" s="7" t="n">
-        <v>0.0106154833357891</v>
+        <v>0.01073</v>
       </c>
       <c r="C64" s="8" t="n">
         <v>0.01284424219848113</v>
       </c>
       <c r="D64" t="n">
-        <v>2681042.9151</v>
+        <v>893680.97</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>0.5139126598474131</v>
+        <v>51.3931</v>
       </c>
       <c r="F64" s="9" t="n">
         <v>5e-05</v>
@@ -5474,6 +8039,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP64" t="n">
+        <v>0.01036</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>0.01083</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>0.01032</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>0.01073</v>
+      </c>
+      <c r="AT64" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5482,16 +8079,16 @@
         </is>
       </c>
       <c r="B65" s="7" t="n">
-        <v>0.0105787223449845</v>
+        <v>0.01049</v>
       </c>
       <c r="C65" s="8" t="n">
         <v>-0.003462959682736577</v>
       </c>
       <c r="D65" t="n">
-        <v>3628560.46566</v>
+        <v>1209520.16</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>0.4083332068026</v>
+        <v>40.9277</v>
       </c>
       <c r="F65" s="9" t="n">
         <v>5e-05</v>
@@ -5546,6 +8143,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP65" t="n">
+        <v>0.01073</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>0.01076</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>0.01032</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>0.01049</v>
+      </c>
+      <c r="AT65" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5554,16 +8183,16 @@
         </is>
       </c>
       <c r="B66" s="7" t="n">
-        <v>0.0108830651158468</v>
+        <v>0.01106</v>
       </c>
       <c r="C66" s="8" t="n">
         <v>0.02876933158252259</v>
       </c>
       <c r="D66" t="n">
-        <v>2804594.84019</v>
+        <v>934864.95</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>0.5059317839174351</v>
+        <v>50.5979</v>
       </c>
       <c r="F66" s="9" t="n">
         <v>5e-05</v>
@@ -5618,6 +8247,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP66" t="n">
+        <v>0.01049</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>0.01046</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>0.01106</v>
+      </c>
+      <c r="AT66" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5626,16 +8287,16 @@
         </is>
       </c>
       <c r="B67" s="7" t="n">
-        <v>0.0112640328798221</v>
+        <v>0.0112</v>
       </c>
       <c r="C67" s="8" t="n">
         <v>0.03500555771007696</v>
       </c>
       <c r="D67" t="n">
-        <v>3139487.93898</v>
+        <v>1046495.98</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>0.4704489141748113</v>
+        <v>47.0391</v>
       </c>
       <c r="F67" s="9" t="n">
         <v>5e-05</v>
@@ -5690,6 +8351,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP67" t="n">
+        <v>0.01105</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>0.01151</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>0.01094</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="AT67" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5698,16 +8391,16 @@
         </is>
       </c>
       <c r="B68" s="7" t="n">
-        <v>0.0111521554821729</v>
+        <v>0.0109</v>
       </c>
       <c r="C68" s="8" t="n">
         <v>-0.009932268384054033</v>
       </c>
       <c r="D68" t="n">
-        <v>7423715.72874</v>
+        <v>2474571.91</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>0.5028265865587382</v>
+        <v>50.3658</v>
       </c>
       <c r="F68" s="9" t="n">
         <v>5e-05</v>
@@ -5762,6 +8455,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP68" t="n">
+        <v>0.01119</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>0.01082</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="AT68" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5770,16 +8495,16 @@
         </is>
       </c>
       <c r="B69" s="7" t="n">
-        <v>0.0101854726452663</v>
+        <v>0.01014</v>
       </c>
       <c r="C69" s="8" t="n">
         <v>-0.08668125533686066</v>
       </c>
       <c r="D69" t="n">
-        <v>6002487.79722</v>
+        <v>2000829.27</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>0.4302550162629961</v>
+        <v>43.0072</v>
       </c>
       <c r="F69" s="9" t="n">
         <v>5e-05</v>
@@ -5834,6 +8559,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP69" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>0.01099</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>0.009769999999999999</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>0.01014</v>
+      </c>
+      <c r="AT69" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5842,16 +8599,16 @@
         </is>
       </c>
       <c r="B70" s="7" t="n">
-        <v>0.0101868967903926</v>
+        <v>0.01</v>
       </c>
       <c r="C70" s="8" t="n">
         <v>0.0001398212116314745</v>
       </c>
       <c r="D70" t="n">
-        <v>5283069.23775</v>
+        <v>1761023.08</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>0.4785911691336653</v>
+        <v>47.9144</v>
       </c>
       <c r="F70" s="9" t="n">
         <v>5e-05</v>
@@ -5912,6 +8669,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP70" t="n">
+        <v>0.01013</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>0.01066</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>0.00984</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AT70" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5920,16 +8709,16 @@
         </is>
       </c>
       <c r="B71" s="7" t="n">
-        <v>0.0097151301627331</v>
+        <v>0.009650000000000001</v>
       </c>
       <c r="C71" s="8" t="n">
         <v>-0.04631112274588167</v>
       </c>
       <c r="D71" t="n">
-        <v>2527157.4921</v>
+        <v>842385.83</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>0.5014086656705108</v>
+        <v>50.1895</v>
       </c>
       <c r="F71" s="9" t="n">
         <v>5e-05</v>
@@ -5990,6 +8779,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP71" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>0.01007</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>0.009429999999999999</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>0.009650000000000001</v>
+      </c>
+      <c r="AT71" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
@@ -5998,16 +8819,16 @@
         </is>
       </c>
       <c r="B72" s="7" t="n">
-        <v>0.0106638989426612</v>
+        <v>0.01062</v>
       </c>
       <c r="C72" s="8" t="n">
         <v>0.09765888506234788</v>
       </c>
       <c r="D72" t="n">
-        <v>9368282.27025</v>
+        <v>3122760.76</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>0.5007405472199268</v>
+        <v>50.0204</v>
       </c>
       <c r="F72" s="9" t="n">
         <v>5e-05</v>
@@ -6068,6 +8889,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP72" t="n">
+        <v>0.009639999999999999</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>0.01118</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>0.00963</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>0.01062</v>
+      </c>
+      <c r="AT72" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6076,16 +8929,16 @@
         </is>
       </c>
       <c r="B73" s="7" t="n">
-        <v>0.0110034399466694</v>
+        <v>0.01162</v>
       </c>
       <c r="C73" s="8" t="n">
         <v>0.03184023084182241</v>
       </c>
       <c r="D73" t="n">
-        <v>4985976.25413</v>
+        <v>1661992.08</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>0.5324543763313582</v>
+        <v>53.1657</v>
       </c>
       <c r="F73" s="9" t="n">
         <v>5e-05</v>
@@ -6146,6 +8999,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP73" t="n">
+        <v>0.01062</v>
+      </c>
+      <c r="AQ73" t="n">
+        <v>0.01183</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>0.01052</v>
+      </c>
+      <c r="AS73" t="n">
+        <v>0.01162</v>
+      </c>
+      <c r="AT73" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6154,16 +9039,16 @@
         </is>
       </c>
       <c r="B74" s="7" t="n">
-        <v>0.0127190961151527</v>
+        <v>0.01276</v>
       </c>
       <c r="C74" s="8" t="n">
         <v>0.1559199829143074</v>
       </c>
       <c r="D74" t="n">
-        <v>42160637.25363</v>
+        <v>14053545.75</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>0.4958442781239701</v>
+        <v>49.6289</v>
       </c>
       <c r="F74" s="9" t="n">
         <v>5e-05</v>
@@ -6218,6 +9103,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP74" t="n">
+        <v>0.01162</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>0.01343</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>0.01147</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>0.01276</v>
+      </c>
+      <c r="AT74" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6226,16 +9143,16 @@
         </is>
       </c>
       <c r="B75" s="7" t="n">
-        <v>0.0123945546200928</v>
+        <v>0.01224</v>
       </c>
       <c r="C75" s="8" t="n">
         <v>-0.02551608165561881</v>
       </c>
       <c r="D75" t="n">
-        <v>14714505.90168</v>
+        <v>4904835.3</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>0.4947042971149267</v>
+        <v>49.5788</v>
       </c>
       <c r="F75" s="9" t="n">
         <v>5e-05</v>
@@ -6296,6 +9213,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP75" t="n">
+        <v>0.01276</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>0.01311</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>0.01165</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>0.01224</v>
+      </c>
+      <c r="AT75" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6304,16 +9253,16 @@
         </is>
       </c>
       <c r="B76" s="7" t="n">
-        <v>0.0122554879139452</v>
+        <v>0.01252</v>
       </c>
       <c r="C76" s="8" t="n">
         <v>-0.01121998413094727</v>
       </c>
       <c r="D76" t="n">
-        <v>6385354.5948</v>
+        <v>2128451.53</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>0.4851541574169817</v>
+        <v>48.5569</v>
       </c>
       <c r="F76" s="9" t="n">
         <v>5e-05</v>
@@ -6368,6 +9317,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP76" t="n">
+        <v>0.01223</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>0.01274</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>0.01169</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>0.01252</v>
+      </c>
+      <c r="AT76" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6376,19 +9357,19 @@
         </is>
       </c>
       <c r="B77" s="7" t="n">
-        <v>0.0126220573957251</v>
+        <v>0.01253</v>
       </c>
       <c r="C77" s="8" t="n">
         <v>0.02991063957256168</v>
       </c>
       <c r="D77" t="n">
-        <v>3913233.89808</v>
+        <v>1304411.3</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>0.4775459666208886</v>
+        <v>47.7718</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>4.035166666666667e-05</v>
+        <v>4.035e-05</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>1.382e-05</v>
@@ -6440,6 +9421,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP77" t="n">
+        <v>0.01253</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>0.01306</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>0.01227</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>0.01253</v>
+      </c>
+      <c r="AT77" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6448,16 +9461,16 @@
         </is>
       </c>
       <c r="B78" s="7" t="n">
-        <v>0.0127757063169024</v>
+        <v>0.01293</v>
       </c>
       <c r="C78" s="8" t="n">
         <v>0.01217304884299919</v>
       </c>
       <c r="D78" t="n">
-        <v>4691117.05773</v>
+        <v>1563705.69</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>0.5223815945124306</v>
+        <v>52.2356</v>
       </c>
       <c r="F78" s="9" t="n">
         <v>5e-05</v>
@@ -6512,6 +9525,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP78" t="n">
+        <v>0.01253</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>0.01339</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>0.01232</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>0.01293</v>
+      </c>
+      <c r="AT78" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6520,16 +9565,16 @@
         </is>
       </c>
       <c r="B79" s="7" t="n">
-        <v>0.0128687859520133</v>
+        <v>0.013</v>
       </c>
       <c r="C79" s="8" t="n">
         <v>0.007285674294794653</v>
       </c>
       <c r="D79" t="n">
-        <v>4130509.36071</v>
+        <v>1376836.45</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>0.4846342837962497</v>
+        <v>48.5087</v>
       </c>
       <c r="F79" s="9" t="n">
         <v>5e-05</v>
@@ -6584,6 +9629,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP79" t="n">
+        <v>0.01293</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>0.01335</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>0.01235</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="AT79" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6592,16 +9669,16 @@
         </is>
       </c>
       <c r="B80" s="7" t="n">
-        <v>0.0129315029847468</v>
+        <v>0.01329</v>
       </c>
       <c r="C80" s="8" t="n">
         <v>0.004873578049037874</v>
       </c>
       <c r="D80" t="n">
-        <v>3842080.41651</v>
+        <v>1280693.47</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>0.4646369148764205</v>
+        <v>46.5028</v>
       </c>
       <c r="F80" s="9" t="n">
         <v>5e-05</v>
@@ -6656,6 +9733,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP80" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>0.01331</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>0.01329</v>
+      </c>
+      <c r="AT80" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6664,16 +9773,16 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>0.0129933109667005</v>
+        <v>0.01336</v>
       </c>
       <c r="C81" s="8" t="n">
         <v>0.004779644100659119</v>
       </c>
       <c r="D81" t="n">
-        <v>2797311.1167</v>
+        <v>932437.04</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>0.474907002301465</v>
+        <v>47.5777</v>
       </c>
       <c r="F81" s="9" t="n">
         <v>5e-05</v>
@@ -6728,6 +9837,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP81" t="n">
+        <v>0.01328</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>0.01337</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>0.01265</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>0.01336</v>
+      </c>
+      <c r="AT81" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6736,16 +9877,16 @@
         </is>
       </c>
       <c r="B82" s="7" t="n">
-        <v>0.0131215841190687</v>
+        <v>0.01302</v>
       </c>
       <c r="C82" s="8" t="n">
         <v>0.009872245241951072</v>
       </c>
       <c r="D82" t="n">
-        <v>1986038.5557</v>
+        <v>662012.85</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>0.487360601979636</v>
+        <v>48.7731</v>
       </c>
       <c r="F82" s="9" t="n">
         <v>5e-05</v>
@@ -6800,6 +9941,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP82" t="n">
+        <v>0.01336</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>0.01343</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>0.01283</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>0.01302</v>
+      </c>
+      <c r="AT82" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6808,16 +9981,16 @@
         </is>
       </c>
       <c r="B83" s="7" t="n">
-        <v>0.0137127678949149</v>
+        <v>0.01424</v>
       </c>
       <c r="C83" s="8" t="n">
         <v>0.04505429912132897</v>
       </c>
       <c r="D83" t="n">
-        <v>7229116.49211</v>
+        <v>2409705.5</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>0.4863269299988212</v>
+        <v>48.8579</v>
       </c>
       <c r="F83" s="9" t="n">
         <v>5e-05</v>
@@ -6872,6 +10045,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP83" t="n">
+        <v>0.01302</v>
+      </c>
+      <c r="AQ83" t="n">
+        <v>0.01465</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>0.01282</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>0.01424</v>
+      </c>
+      <c r="AT83" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6880,16 +10085,16 @@
         </is>
       </c>
       <c r="B84" s="7" t="n">
-        <v>0.0151582139744361</v>
+        <v>0.01508</v>
       </c>
       <c r="C84" s="8" t="n">
         <v>0.1054087760106561</v>
       </c>
       <c r="D84" t="n">
-        <v>15798076.95924</v>
+        <v>5266025.65</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>0.4939927377672475</v>
+        <v>49.3803</v>
       </c>
       <c r="F84" s="9" t="n">
         <v>5e-05</v>
@@ -6944,6 +10149,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP84" t="n">
+        <v>0.01426</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>0.01576</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>0.01423</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>0.01508</v>
+      </c>
+      <c r="AT84" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6952,16 +10189,16 @@
         </is>
       </c>
       <c r="B85" s="7" t="n">
-        <v>0.0144410590749155</v>
+        <v>0.01373</v>
       </c>
       <c r="C85" s="8" t="n">
         <v>-0.04731130598433697</v>
       </c>
       <c r="D85" t="n">
-        <v>7489591.783199999</v>
+        <v>2496530.59</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>0.4255644779297824</v>
+        <v>42.7169</v>
       </c>
       <c r="F85" s="9" t="n">
         <v>5e-05</v>
@@ -7016,6 +10253,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP85" t="n">
+        <v>0.01507</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>0.01538</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>0.01358</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>0.01373</v>
+      </c>
+      <c r="AT85" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7024,16 +10293,16 @@
         </is>
       </c>
       <c r="B86" s="7" t="n">
-        <v>0.0138668068431125</v>
+        <v>0.01404</v>
       </c>
       <c r="C86" s="8" t="n">
         <v>-0.03976524358940481</v>
       </c>
       <c r="D86" t="n">
-        <v>4028568.7911</v>
+        <v>1342856.26</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>0.491487073931736</v>
+        <v>49.1858</v>
       </c>
       <c r="F86" s="9" t="n">
         <v>5e-05</v>
@@ -7088,6 +10357,38 @@
           <t>freshwatch/derived_1h+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP86" t="n">
+        <v>0.01372</v>
+      </c>
+      <c r="AQ86" t="n">
+        <v>0.01464</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>0.01332</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>0.01404</v>
+      </c>
+      <c r="AT86" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -7102,23 +10403,39 @@
         <v>0.06657575657701176</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>1170752.06643</v>
+        <v>1170752.07</v>
       </c>
       <c r="E87" s="6" t="n">
-        <v>0.4897097148650797</v>
-      </c>
-      <c r="F87" s="4" t="n"/>
-      <c r="G87" s="4" t="n"/>
-      <c r="H87" s="4" t="n"/>
-      <c r="I87" s="4" t="n"/>
+        <v>48.9941</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I87" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J87" s="4" t="n"/>
       <c r="K87" s="4" t="n"/>
-      <c r="L87" s="4" t="n"/>
+      <c r="L87" s="4" t="n">
+        <v>3482365.02588</v>
+      </c>
       <c r="M87" s="4" t="n"/>
       <c r="N87" s="4" t="n"/>
-      <c r="O87" s="4" t="n"/>
-      <c r="P87" s="4" t="n"/>
-      <c r="Q87" s="4" t="n"/>
+      <c r="O87" s="4" t="n">
+        <v>4.9735</v>
+      </c>
+      <c r="P87" s="4" t="n">
+        <v>2.3456</v>
+      </c>
+      <c r="Q87" s="4" t="n">
+        <v>1.8217</v>
+      </c>
       <c r="R87" s="4" t="n"/>
       <c r="S87" s="4" t="n"/>
       <c r="T87" s="4" t="n"/>
@@ -7161,6 +10478,38 @@
           <t>fapi_klines_only+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP87" t="n">
+        <v>0.01404</v>
+      </c>
+      <c r="AQ87" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>0.01374</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>0.01479</v>
+      </c>
+      <c r="AT87" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -7175,23 +10524,39 @@
         <v>0.03651115618661271</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>2138841.97782</v>
+        <v>2138841.98</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>0.4921583871518967</v>
-      </c>
-      <c r="F88" s="4" t="n"/>
-      <c r="G88" s="4" t="n"/>
-      <c r="H88" s="4" t="n"/>
-      <c r="I88" s="4" t="n"/>
+        <v>49.2429</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J88" s="4" t="n"/>
       <c r="K88" s="4" t="n"/>
-      <c r="L88" s="4" t="n"/>
+      <c r="L88" s="4" t="n">
+        <v>3777764.24122795</v>
+      </c>
       <c r="M88" s="4" t="n"/>
       <c r="N88" s="4" t="n"/>
-      <c r="O88" s="4" t="n"/>
-      <c r="P88" s="4" t="n"/>
-      <c r="Q88" s="4" t="n"/>
+      <c r="O88" s="4" t="n">
+        <v>4.4324</v>
+      </c>
+      <c r="P88" s="4" t="n">
+        <v>2.3245</v>
+      </c>
+      <c r="Q88" s="4" t="n">
+        <v>1.7847</v>
+      </c>
       <c r="R88" s="4" t="n"/>
       <c r="S88" s="4" t="n"/>
       <c r="T88" s="4" t="n"/>
@@ -7234,6 +10599,38 @@
           <t>fapi_klines_only+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP88" t="n">
+        <v>0.01478</v>
+      </c>
+      <c r="AQ88" t="n">
+        <v>0.01598</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>0.01465</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>0.01533</v>
+      </c>
+      <c r="AT88" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -7248,23 +10645,39 @@
         <v>0.05805609915198939</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>1208319.74082</v>
+        <v>1208319.74</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>0.4852820696871226</v>
-      </c>
-      <c r="F89" s="4" t="n"/>
-      <c r="G89" s="4" t="n"/>
-      <c r="H89" s="4" t="n"/>
-      <c r="I89" s="4" t="n"/>
+        <v>48.5973</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H89" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I89" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J89" s="4" t="n"/>
       <c r="K89" s="4" t="n"/>
-      <c r="L89" s="4" t="n"/>
+      <c r="L89" s="4" t="n">
+        <v>4006488.80909558</v>
+      </c>
       <c r="M89" s="4" t="n"/>
       <c r="N89" s="4" t="n"/>
-      <c r="O89" s="4" t="n"/>
-      <c r="P89" s="4" t="n"/>
-      <c r="Q89" s="4" t="n"/>
+      <c r="O89" s="4" t="n">
+        <v>4.1925</v>
+      </c>
+      <c r="P89" s="4" t="n">
+        <v>2.465</v>
+      </c>
+      <c r="Q89" s="4" t="n">
+        <v>1.8977</v>
+      </c>
       <c r="R89" s="4" t="n"/>
       <c r="S89" s="4" t="n"/>
       <c r="T89" s="4" t="n"/>
@@ -7307,6 +10720,38 @@
           <t>fapi_klines_only+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP89" t="n">
+        <v>0.01533</v>
+      </c>
+      <c r="AQ89" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="AR89" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>0.01622</v>
+      </c>
+      <c r="AT89" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7315,16 +10760,16 @@
         </is>
       </c>
       <c r="B90" s="7" t="n">
-        <v>0.0157116977509727</v>
+        <v>0.01489</v>
       </c>
       <c r="C90" s="8" t="n">
         <v>-0.03133799315827979</v>
       </c>
       <c r="D90" t="n">
-        <v>1525598.54568</v>
+        <v>1485553.61</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>0.4796815651178521</v>
+        <v>48.0604</v>
       </c>
       <c r="F90" s="9" t="n">
         <v>5e-05</v>
@@ -7379,6 +10824,38 @@
           <t>freshwatch/native_1d+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP90" t="n">
+        <v>0.01621</v>
+      </c>
+      <c r="AQ90" t="n">
+        <v>0.01631</v>
+      </c>
+      <c r="AR90" t="n">
+        <v>0.01478</v>
+      </c>
+      <c r="AS90" t="n">
+        <v>0.01489</v>
+      </c>
+      <c r="AT90" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7387,16 +10864,16 @@
         </is>
       </c>
       <c r="B91" s="7" t="n">
-        <v>0.0138861616835604</v>
+        <v>0.01448</v>
       </c>
       <c r="C91" s="8" t="n">
         <v>-0.1161896121187338</v>
       </c>
       <c r="D91" t="n">
-        <v>2429507.24011</v>
+        <v>2429507.24</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>0.4502473886750961</v>
+        <v>45.0652</v>
       </c>
       <c r="F91" s="9" t="n">
         <v>5e-05</v>
@@ -7451,6 +10928,38 @@
           <t>freshwatch/native_1d+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP91" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="AQ91" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AR91" t="n">
+        <v>0.01309</v>
+      </c>
+      <c r="AS91" t="n">
+        <v>0.01448</v>
+      </c>
+      <c r="AT91" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7459,16 +10968,16 @@
         </is>
       </c>
       <c r="B92" s="7" t="n">
-        <v>0.0146583605901685</v>
+        <v>0.01439</v>
       </c>
       <c r="C92" s="8" t="n">
         <v>0.05560924063863482</v>
       </c>
       <c r="D92" t="n">
-        <v>2232808.37719</v>
+        <v>2232808.38</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>0.5096597038344611</v>
+        <v>50.9911</v>
       </c>
       <c r="F92" s="9" t="n">
         <v>5e-05</v>
@@ -7523,6 +11032,38 @@
           <t>freshwatch/native_1d+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP92" t="n">
+        <v>0.01448</v>
+      </c>
+      <c r="AQ92" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="AR92" t="n">
+        <v>0.01418</v>
+      </c>
+      <c r="AS92" t="n">
+        <v>0.01439</v>
+      </c>
+      <c r="AT92" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7531,16 +11072,16 @@
         </is>
       </c>
       <c r="B93" s="7" t="n">
-        <v>0.0145956569346365</v>
+        <v>0.01506</v>
       </c>
       <c r="C93" s="8" t="n">
         <v>-0.004277671786438009</v>
       </c>
       <c r="D93" t="n">
-        <v>1129865.12875</v>
+        <v>1129865.13</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>0.4758360415137855</v>
+        <v>47.6916</v>
       </c>
       <c r="F93" s="9" t="n">
         <v>5e-05</v>
@@ -7595,6 +11136,38 @@
           <t>freshwatch/native_1d+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP93" t="n">
+        <v>0.01439</v>
+      </c>
+      <c r="AQ93" t="n">
+        <v>0.01518</v>
+      </c>
+      <c r="AR93" t="n">
+        <v>0.01392</v>
+      </c>
+      <c r="AS93" t="n">
+        <v>0.01506</v>
+      </c>
+      <c r="AT93" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7603,16 +11176,16 @@
         </is>
       </c>
       <c r="B94" s="7" t="n">
-        <v>0.01560017891656453</v>
+        <v>0.0161</v>
       </c>
       <c r="C94" s="8" t="n">
         <v>0.06882334837181792</v>
       </c>
       <c r="D94" t="n">
-        <v>2392917.38768</v>
+        <v>2392917.39</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>0.5152220283110335</v>
+        <v>51.4904</v>
       </c>
       <c r="F94" s="9" t="n">
         <v>5e-05</v>
@@ -7667,6 +11240,38 @@
           <t>freshwatch/native_1d+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP94" t="n">
+        <v>0.01505</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>0.01673</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>0.01461</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="AT94" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7675,16 +11280,16 @@
         </is>
       </c>
       <c r="B95" s="7" t="n">
-        <v>0.0173537118053967</v>
+        <v>0.01752</v>
       </c>
       <c r="C95" s="8" t="n">
         <v>0.1124046652420276</v>
       </c>
       <c r="D95" t="n">
-        <v>9821946.806159999</v>
+        <v>9821946.810000001</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>0.5199692780337942</v>
+        <v>52.0017</v>
       </c>
       <c r="F95" s="9" t="n">
         <v>5e-05</v>
@@ -7739,6 +11344,38 @@
           <t>freshwatch/native_1d+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP95" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="AQ95" t="n">
+        <v>0.01863</v>
+      </c>
+      <c r="AR95" t="n">
+        <v>0.01563</v>
+      </c>
+      <c r="AS95" t="n">
+        <v>0.01752</v>
+      </c>
+      <c r="AT95" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7747,16 +11384,16 @@
         </is>
       </c>
       <c r="B96" s="7" t="n">
-        <v>0.0174107849275162</v>
+        <v>0.01757</v>
       </c>
       <c r="C96" s="8" t="n">
         <v>0.003288813526438172</v>
       </c>
       <c r="D96" t="n">
-        <v>3062632.03959</v>
+        <v>3062632.04</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>0.4758635148592693</v>
+        <v>47.6071</v>
       </c>
       <c r="F96" s="9" t="n">
         <v>5e-05</v>
@@ -7817,6 +11454,38 @@
           <t>freshwatch/native_1d+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP96" t="n">
+        <v>0.01753</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>0.01805</v>
+      </c>
+      <c r="AR96" t="n">
+        <v>0.01682</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>0.01757</v>
+      </c>
+      <c r="AT96" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7825,16 +11494,16 @@
         </is>
       </c>
       <c r="B97" s="7" t="n">
-        <v>0.0198572556607966</v>
+        <v>0.02038</v>
       </c>
       <c r="C97" s="8" t="n">
         <v>0.1405146719958597</v>
       </c>
       <c r="D97" t="n">
-        <v>17947839.00635</v>
+        <v>17947839.01</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>0.5265599848499195</v>
+        <v>52.7241</v>
       </c>
       <c r="F97" s="9" t="n">
         <v>5e-05</v>
@@ -7889,6 +11558,38 @@
           <t>freshwatch/native_1d+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP97" t="n">
+        <v>0.01757</v>
+      </c>
+      <c r="AQ97" t="n">
+        <v>0.0224</v>
+      </c>
+      <c r="AR97" t="n">
+        <v>0.01704</v>
+      </c>
+      <c r="AS97" t="n">
+        <v>0.02038</v>
+      </c>
+      <c r="AT97" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7897,19 +11598,19 @@
         </is>
       </c>
       <c r="B98" s="7" t="n">
-        <v>0.02249147507766923</v>
+        <v>0.02157</v>
       </c>
       <c r="C98" s="8" t="n">
         <v>0.1326577781880134</v>
       </c>
       <c r="D98" t="n">
-        <v>33252326.46244</v>
+        <v>33252326.46</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>0.4863365522909389</v>
+        <v>48.6201</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>4.262666666666667e-05</v>
+        <v>4.263e-05</v>
       </c>
       <c r="G98" s="9" t="n">
         <v>1.22e-05</v>
@@ -7967,6 +11668,38 @@
           <t>freshwatch/native_1d+spot_klines_Binance</t>
         </is>
       </c>
+      <c r="AP98" t="n">
+        <v>0.02038</v>
+      </c>
+      <c r="AQ98" t="n">
+        <v>0.02442</v>
+      </c>
+      <c r="AR98" t="n">
+        <v>0.02033</v>
+      </c>
+      <c r="AS98" t="n">
+        <v>0.02157</v>
+      </c>
+      <c r="AT98" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -7975,33 +11708,47 @@
         </is>
       </c>
       <c r="B99" s="5" t="n">
-        <v>0.02388</v>
+        <v>0.02865</v>
       </c>
       <c r="C99" s="6" t="n">
         <v>0.06173560949363321</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>4183934.48404</v>
+        <v>24157156.87</v>
       </c>
       <c r="E99" s="6" t="n">
-        <v>0.5123260206201369</v>
-      </c>
-      <c r="F99" s="4" t="n"/>
-      <c r="G99" s="4" t="n"/>
-      <c r="H99" s="4" t="n"/>
-      <c r="I99" s="4" t="n"/>
+        <v>51.9434</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>4.199e-05</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>2.529e-05</v>
+      </c>
+      <c r="H99" s="4" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I99" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J99" s="4" t="n"/>
       <c r="K99" s="4" t="n"/>
       <c r="L99" s="4" t="n">
-        <v>7102250.21244</v>
+        <v>6343786.63257</v>
       </c>
       <c r="M99" s="4" t="n"/>
       <c r="N99" s="4" t="n">
         <v>3.694850543275284</v>
       </c>
-      <c r="O99" s="4" t="n"/>
-      <c r="P99" s="4" t="n"/>
-      <c r="Q99" s="4" t="n"/>
+      <c r="O99" s="4" t="n">
+        <v>2.0739</v>
+      </c>
+      <c r="P99" s="4" t="n">
+        <v>1.192</v>
+      </c>
+      <c r="Q99" s="4" t="n">
+        <v>1.1119</v>
+      </c>
       <c r="R99" s="4" t="n"/>
       <c r="S99" s="4" t="n"/>
       <c r="T99" s="4" t="n"/>
@@ -8042,6 +11789,1118 @@
       <c r="AO99" s="4" t="inlineStr">
         <is>
           <t>fapi_klines+oi_rt+spot_klines_Binance</t>
+        </is>
+      </c>
+      <c r="AP99" t="n">
+        <v>0.02156</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>0.02973</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>0.02114</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>0.02865</v>
+      </c>
+      <c r="AT99" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="D100" t="n">
+        <v>23750950.16</v>
+      </c>
+      <c r="E100" t="n">
+        <v>49.0107</v>
+      </c>
+      <c r="F100" t="n">
+        <v>2.012e-05</v>
+      </c>
+      <c r="G100" t="n">
+        <v>-5.857e-05</v>
+      </c>
+      <c r="H100" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I100" t="n">
+        <v>6</v>
+      </c>
+      <c r="L100" t="n">
+        <v>7873422.96225</v>
+      </c>
+      <c r="O100" t="n">
+        <v>2.2014</v>
+      </c>
+      <c r="P100" t="n">
+        <v>1.2727</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>1.2878</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>0.02866</v>
+      </c>
+      <c r="AQ100" t="n">
+        <v>0.03133</v>
+      </c>
+      <c r="AR100" t="n">
+        <v>0.02427</v>
+      </c>
+      <c r="AS100" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="AT100" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>0.03895</v>
+      </c>
+      <c r="D101" t="n">
+        <v>62002007.57</v>
+      </c>
+      <c r="E101" t="n">
+        <v>50.7051</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1.584e-05</v>
+      </c>
+      <c r="G101" t="n">
+        <v>-4.149e-05</v>
+      </c>
+      <c r="H101" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I101" t="n">
+        <v>6</v>
+      </c>
+      <c r="L101" t="n">
+        <v>5830123.61774658</v>
+      </c>
+      <c r="O101" t="n">
+        <v>2.7836</v>
+      </c>
+      <c r="P101" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>1.2758</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>0.02449</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>0.04047</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>0.02407</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>0.03895</v>
+      </c>
+      <c r="AT101" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0.10907</v>
+      </c>
+      <c r="D102" t="n">
+        <v>844366000.54</v>
+      </c>
+      <c r="E102" t="n">
+        <v>52.2531</v>
+      </c>
+      <c r="F102" t="n">
+        <v>3.376e-05</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1.547e-05</v>
+      </c>
+      <c r="H102" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I102" t="n">
+        <v>6</v>
+      </c>
+      <c r="L102" t="n">
+        <v>10542658.1499</v>
+      </c>
+      <c r="O102" t="n">
+        <v>1.3087</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0.8965</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0.9095</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>0.03896</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>0.11734</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>0.03553</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>0.10907</v>
+      </c>
+      <c r="AT102" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>0.20192</v>
+      </c>
+      <c r="D103" t="n">
+        <v>2295631241.52</v>
+      </c>
+      <c r="E103" t="n">
+        <v>51.1802</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.00056074</v>
+      </c>
+      <c r="G103" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.00144695</v>
+      </c>
+      <c r="I103" t="n">
+        <v>6</v>
+      </c>
+      <c r="L103" t="n">
+        <v>48355967.71878271</v>
+      </c>
+      <c r="O103" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0.4501</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>0.1091</v>
+      </c>
+      <c r="AQ103" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="AR103" t="n">
+        <v>0.0927</v>
+      </c>
+      <c r="AS103" t="n">
+        <v>0.20192</v>
+      </c>
+      <c r="AT103" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>0.10779</v>
+      </c>
+      <c r="D104" t="n">
+        <v>887566087.9</v>
+      </c>
+      <c r="E104" t="n">
+        <v>50.0154</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.00045311</v>
+      </c>
+      <c r="G104" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.00127318</v>
+      </c>
+      <c r="I104" t="n">
+        <v>6</v>
+      </c>
+      <c r="L104" t="n">
+        <v>62019942.17934986</v>
+      </c>
+      <c r="O104" t="n">
+        <v>1.5757</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0.4963</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0.5873</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>0.20191</v>
+      </c>
+      <c r="AQ104" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AR104" t="n">
+        <v>0.10666</v>
+      </c>
+      <c r="AS104" t="n">
+        <v>0.10779</v>
+      </c>
+      <c r="AT104" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>0.07653</v>
+      </c>
+      <c r="D105" t="n">
+        <v>384304070.06</v>
+      </c>
+      <c r="E105" t="n">
+        <v>50.5408</v>
+      </c>
+      <c r="F105" t="n">
+        <v>6.918e-05</v>
+      </c>
+      <c r="G105" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.00011712</v>
+      </c>
+      <c r="I105" t="n">
+        <v>6</v>
+      </c>
+      <c r="L105" t="n">
+        <v>30636600.94839</v>
+      </c>
+      <c r="O105" t="n">
+        <v>1.6889</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0.7562</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0.7325</v>
+      </c>
+      <c r="AP105" t="n">
+        <v>0.1078</v>
+      </c>
+      <c r="AQ105" t="n">
+        <v>0.12148</v>
+      </c>
+      <c r="AR105" t="n">
+        <v>0.07503</v>
+      </c>
+      <c r="AS105" t="n">
+        <v>0.07653</v>
+      </c>
+      <c r="AT105" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>0.06698999999999999</v>
+      </c>
+      <c r="D106" t="n">
+        <v>344492613.97</v>
+      </c>
+      <c r="E106" t="n">
+        <v>50.861</v>
+      </c>
+      <c r="F106" t="n">
+        <v>8.977e-05</v>
+      </c>
+      <c r="G106" t="n">
+        <v>-2.19e-06</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.00031509</v>
+      </c>
+      <c r="I106" t="n">
+        <v>6</v>
+      </c>
+      <c r="L106" t="n">
+        <v>20926634.52396244</v>
+      </c>
+      <c r="O106" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0.8339</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>0.07653</v>
+      </c>
+      <c r="AQ106" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AR106" t="n">
+        <v>0.0613</v>
+      </c>
+      <c r="AS106" t="n">
+        <v>0.06698999999999999</v>
+      </c>
+      <c r="AT106" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>0.03529</v>
+      </c>
+      <c r="D107" t="n">
+        <v>224371600.7</v>
+      </c>
+      <c r="E107" t="n">
+        <v>49.0632</v>
+      </c>
+      <c r="F107" t="n">
+        <v>2.027e-05</v>
+      </c>
+      <c r="G107" t="n">
+        <v>-4.174e-05</v>
+      </c>
+      <c r="H107" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I107" t="n">
+        <v>6</v>
+      </c>
+      <c r="L107" t="n">
+        <v>17860417.01160542</v>
+      </c>
+      <c r="O107" t="n">
+        <v>1.527</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0.9677</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>0.06701</v>
+      </c>
+      <c r="AQ107" t="n">
+        <v>0.0693</v>
+      </c>
+      <c r="AR107" t="n">
+        <v>0.03411</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>0.03529</v>
+      </c>
+      <c r="AT107" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0.02968</v>
+      </c>
+      <c r="D108" t="n">
+        <v>234184652.21</v>
+      </c>
+      <c r="E108" t="n">
+        <v>50.2346</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.46e-05</v>
+      </c>
+      <c r="G108" t="n">
+        <v>-5.873e-05</v>
+      </c>
+      <c r="H108" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I108" t="n">
+        <v>6</v>
+      </c>
+      <c r="L108" t="n">
+        <v>12475108.79551</v>
+      </c>
+      <c r="O108" t="n">
+        <v>1.3274</v>
+      </c>
+      <c r="P108" t="n">
+        <v>1.2477</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>1.0446</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>0.03529</v>
+      </c>
+      <c r="AQ108" t="n">
+        <v>0.04324</v>
+      </c>
+      <c r="AR108" t="n">
+        <v>0.02846</v>
+      </c>
+      <c r="AS108" t="n">
+        <v>0.02968</v>
+      </c>
+      <c r="AT108" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0.03318</v>
+      </c>
+      <c r="D109" t="n">
+        <v>128408524.74</v>
+      </c>
+      <c r="E109" t="n">
+        <v>49.5145</v>
+      </c>
+      <c r="F109" t="n">
+        <v>-3.526e-05</v>
+      </c>
+      <c r="G109" t="n">
+        <v>-0.00023174</v>
+      </c>
+      <c r="H109" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I109" t="n">
+        <v>6</v>
+      </c>
+      <c r="L109" t="n">
+        <v>11860042.8184</v>
+      </c>
+      <c r="O109" t="n">
+        <v>1.3743</v>
+      </c>
+      <c r="P109" t="n">
+        <v>1.6399</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>1.3084</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>0.02967</v>
+      </c>
+      <c r="AQ109" t="n">
+        <v>0.03854</v>
+      </c>
+      <c r="AR109" t="n">
+        <v>0.0288</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>0.03318</v>
+      </c>
+      <c r="AT109" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>0.03427</v>
+      </c>
+      <c r="D110" t="n">
+        <v>64446561.43</v>
+      </c>
+      <c r="E110" t="n">
+        <v>49.2851</v>
+      </c>
+      <c r="F110" t="n">
+        <v>-1.4e-06</v>
+      </c>
+      <c r="G110" t="n">
+        <v>-0.00013699</v>
+      </c>
+      <c r="H110" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I110" t="n">
+        <v>6</v>
+      </c>
+      <c r="L110" t="n">
+        <v>12301000.43539458</v>
+      </c>
+      <c r="O110" t="n">
+        <v>1.3497</v>
+      </c>
+      <c r="P110" t="n">
+        <v>1.6483</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>1.3747</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>0.03319</v>
+      </c>
+      <c r="AQ110" t="n">
+        <v>0.03459</v>
+      </c>
+      <c r="AR110" t="n">
+        <v>0.02888</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>0.03427</v>
+      </c>
+      <c r="AT110" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0.04635</v>
+      </c>
+      <c r="D111" t="n">
+        <v>392091511.22</v>
+      </c>
+      <c r="E111" t="n">
+        <v>49.8165</v>
+      </c>
+      <c r="F111" t="n">
+        <v>3.696e-05</v>
+      </c>
+      <c r="G111" t="n">
+        <v>-1.131e-05</v>
+      </c>
+      <c r="H111" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I111" t="n">
+        <v>6</v>
+      </c>
+      <c r="L111" t="n">
+        <v>11910221.32587</v>
+      </c>
+      <c r="O111" t="n">
+        <v>1.3512</v>
+      </c>
+      <c r="P111" t="n">
+        <v>1.4857</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>1.2252</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>0.03428</v>
+      </c>
+      <c r="AQ111" t="n">
+        <v>0.0606</v>
+      </c>
+      <c r="AR111" t="n">
+        <v>0.03305</v>
+      </c>
+      <c r="AS111" t="n">
+        <v>0.04635</v>
+      </c>
+      <c r="AT111" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0.04084</v>
+      </c>
+      <c r="D112" t="n">
+        <v>223633312.12</v>
+      </c>
+      <c r="E112" t="n">
+        <v>49.1758</v>
+      </c>
+      <c r="F112" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G112" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H112" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I112" t="n">
+        <v>6</v>
+      </c>
+      <c r="L112" t="n">
+        <v>16026922.51687176</v>
+      </c>
+      <c r="O112" t="n">
+        <v>1.6582</v>
+      </c>
+      <c r="P112" t="n">
+        <v>1.3546</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>1.3063</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>0.04636</v>
+      </c>
+      <c r="AQ112" t="n">
+        <v>0.05166</v>
+      </c>
+      <c r="AR112" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="AS112" t="n">
+        <v>0.04084</v>
+      </c>
+      <c r="AT112" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0.03261</v>
+      </c>
+      <c r="D113" t="n">
+        <v>64859075.45</v>
+      </c>
+      <c r="E113" t="n">
+        <v>47.2073</v>
+      </c>
+      <c r="F113" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G113" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H113" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I113" t="n">
+        <v>6</v>
+      </c>
+      <c r="L113" t="n">
+        <v>13470038.37887937</v>
+      </c>
+      <c r="O113" t="n">
+        <v>1.7202</v>
+      </c>
+      <c r="P113" t="n">
+        <v>1.4704</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>1.3419</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>0.04085</v>
+      </c>
+      <c r="AQ113" t="n">
+        <v>0.04201</v>
+      </c>
+      <c r="AR113" t="n">
+        <v>0.03219</v>
+      </c>
+      <c r="AS113" t="n">
+        <v>0.03261</v>
+      </c>
+      <c r="AT113" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0.03277</v>
+      </c>
+      <c r="D114" t="n">
+        <v>65082825.42</v>
+      </c>
+      <c r="E114" t="n">
+        <v>48.5415</v>
+      </c>
+      <c r="F114" t="n">
+        <v>4.198e-05</v>
+      </c>
+      <c r="G114" t="n">
+        <v>8.569999999999999e-06</v>
+      </c>
+      <c r="H114" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="I114" t="n">
+        <v>6</v>
+      </c>
+      <c r="L114" t="n">
+        <v>10701407.90140744</v>
+      </c>
+      <c r="O114" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="P114" t="n">
+        <v>1.4201</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>1.1022</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>0.03261</v>
+      </c>
+      <c r="AQ114" t="n">
+        <v>0.03599</v>
+      </c>
+      <c r="AR114" t="n">
+        <v>0.02934</v>
+      </c>
+      <c r="AS114" t="n">
+        <v>0.03277</v>
+      </c>
+      <c r="AT114" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_TUT.xlsx
+++ b/docs/case_files/CASE_TUT.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1033,6 +1033,80 @@
       <c r="B57" t="inlineStr">
         <is>
           <t>cols 42-45 = o/h/l/c append (append-only per L-57 R4) · cols 46-47 = vol_alpha/taker_alpha CHƯA-TRA (chờ nhịp 2 R5) · cols 51-52 = vol_spot_ext_usd/spot_ext_venue CHƯA-TRA (chờ nhịp 2 R5) · cols 48-50 reserved. Cột v1 cũ (1-41) KHÔNG đè.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>META (V5 21/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>schema_version</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>v1+ext-20260821 (v1 cols 1-41 + R4 append cols 42-52 · o/h/l/c + vol_alpha CHƯA-TRA + cols 51-52 CHƯA-TRA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>consumer_rule</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Consumer đọc theo HEADER row 2 field names (không hardcode col index). Cols 42+ append-only per L-57.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>LAYER COVERAGE UPDATE (V4 21/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>lsr_null_dates (57)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-05-01, 2026-05-02, 2026-05-03, 2026-05-04, 2026-05-05, 2026-05-06, 2026-05-07, 2026-05-08, 2026-05-09, 2026-05-10, 2026-05-11, 2026-05-12, 2026-05-13, 2026-05-14, 2026-05-15, 2026-05-16, 2026-05-17, 2026-05-18, 2026-05-19, 2026-05-20, 2026-05-21, 2026-05-22, 2026-05-23, 2026-05-24, 2026-05-25, 2026-05-26, 2026-05-27, 2026-05-28, 2026-05-29, 2026-05-30, 2026-05-31, 2026-06-01, 2026-06-02, 2026-06-03, 2026-06-04, 2026-06-05, 2026-06-06, 2026-06-07, 2026-06-08, 2026-06-09, 2026-06-10, 2026-06-11, 2026-06-12, 2026-06-13, 2026-06-14, 2026-06-15, 2026-06-16, 2026-06-17, 2026-06-18, 2026-06-19, 2026-06-20, 2026-06-21, 2026-06-22, 2026-06-23, 2026-06-24, 2026-06-25, 2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>OI first_nn (real)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>OI last_nn</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -1351,9 +1425,6 @@
           <t>taker_alpha</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr">
         <is>
           <t>vol_spot_ext_usd</t>
